--- a/INSTANCES/instances_xlsx/A_MTN_5/224FL_10A_5.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_5/224FL_10A_5.xlsx
@@ -7522,7 +7522,7 @@
         <v>0</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -7556,7 +7556,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -7607,7 +7607,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -7641,7 +7641,7 @@
         <v>0</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -7658,7 +7658,7 @@
         <v>0</v>
       </c>
       <c r="D10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>1</v>
